--- a/data/trans_orig/IP18A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77529</t>
+          <t>77481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87741</t>
+          <t>87647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>72902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81889</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154291</t>
+          <t>153272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167420</t>
+          <t>167147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>68960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>76739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>62986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71561</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136185</t>
+          <t>135183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147110</t>
+          <t>146697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>58523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75473</t>
+          <t>75435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82818</t>
+          <t>82859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130006</t>
+          <t>129404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140306</t>
+          <t>139984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149317</t>
+          <t>149908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161856</t>
+          <t>161739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154071</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165502</t>
+          <t>165026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>306430</t>
+          <t>306212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324761</t>
+          <t>325013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72078</t>
+          <t>72259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81135</t>
+          <t>81128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>91300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166497</t>
+          <t>167210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>179216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62492</t>
+          <t>62327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>68027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54035</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62364</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119061</t>
+          <t>119283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129203</t>
+          <t>129135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38759</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59739</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40144</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62322</t>
+          <t>62147</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115942</t>
+          <t>113481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502181</t>
+          <t>501643</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>523161</t>
+          <t>522860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530206</t>
+          <t>530381</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>552384</t>
+          <t>551973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1038506</t>
+          <t>1040967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1069730</t>
+          <t>1070564</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64281</t>
+          <t>64575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72941</t>
+          <t>72738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82141</t>
+          <t>82151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>140815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155019</t>
+          <t>155433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>76800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>85788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71294</t>
+          <t>71893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>81972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152434</t>
+          <t>152333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165390</t>
+          <t>165571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66622</t>
+          <t>66533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75875</t>
+          <t>75922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71309</t>
+          <t>70856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79692</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141403</t>
+          <t>141584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153721</t>
+          <t>153685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51870</t>
+          <t>52815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164892</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179157</t>
+          <t>178777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186140</t>
+          <t>185155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200836</t>
+          <t>199661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356009</t>
+          <t>355064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375451</t>
+          <t>375144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119240</t>
+          <t>118548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129637</t>
+          <t>129462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110253</t>
+          <t>109852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122551</t>
+          <t>122863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234187</t>
+          <t>232851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249922</t>
+          <t>249814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42921</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50582</t>
+          <t>50612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57461</t>
+          <t>57952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104097</t>
+          <t>103551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114754</t>
+          <t>114881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>51326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82137</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112350</t>
+          <t>114088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150877</t>
+          <t>148906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556506</t>
+          <t>556459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>581718</t>
+          <t>581613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>591708</t>
+          <t>591398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618448</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1155907</t>
+          <t>1157878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1194434</t>
+          <t>1192696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>22129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>63870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72198</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>78788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88144</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147064</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>158930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>79147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90302</t>
+          <t>90086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83713</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>93458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167083</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181262</t>
+          <t>180751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43016</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50083</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>53071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62310</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99189</t>
+          <t>99477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111133</t>
+          <t>110982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48206</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179200</t>
+          <t>179825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193039</t>
+          <t>193415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161818</t>
+          <t>161014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175681</t>
+          <t>174820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345713</t>
+          <t>346591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365250</t>
+          <t>365020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107474</t>
+          <t>107587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117094</t>
+          <t>117128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119392</t>
+          <t>119536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>126191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230917</t>
+          <t>231007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242330</t>
+          <t>242455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58823</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95846</t>
+          <t>95974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108294</t>
+          <t>108241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46851</t>
+          <t>47630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>71930</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>96503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131190</t>
+          <t>130409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>537636</t>
+          <t>537204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>562283</t>
+          <t>561504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>568988</t>
+          <t>568963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>591803</t>
+          <t>591914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1113932</t>
+          <t>1114713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1147025</t>
+          <t>1148619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>37265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>62069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69360</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49593</t>
+          <t>49523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86150</t>
+          <t>86644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94836</t>
+          <t>94840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121929</t>
+          <t>121173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128244</t>
+          <t>128081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211281</t>
+          <t>210498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222069</t>
+          <t>221728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
